--- a/九龙-观塘南部-Bal Residence/Bal Residence_销控明细表.xlsx
+++ b/九龙-观塘南部-Bal Residence/Bal Residence_销控明细表.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -635,10 +635,14 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -696,6 +700,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -731,7 +755,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -742,6 +766,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>6160800</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>16170</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -777,7 +817,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -788,6 +828,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>16793</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -823,7 +879,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -834,6 +890,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>14100000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>17803</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -869,7 +941,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -880,6 +952,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6165700</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>16183</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -915,7 +1003,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -926,6 +1014,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5453800</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>16088</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -961,7 +1065,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -972,6 +1076,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5239600</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>15013</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1007,7 +1127,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1018,6 +1138,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7450300</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>15236</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1053,7 +1189,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1064,6 +1200,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7451100</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>15237</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1099,7 +1251,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1110,6 +1262,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5239600</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>15231</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1145,7 +1313,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1156,6 +1324,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5442600</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>16102</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1191,7 +1375,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1202,6 +1386,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5801900</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>17115</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1237,7 +1437,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1248,6 +1448,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5209900</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>14928</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1283,7 +1499,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1294,6 +1510,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7669900</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>15685</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1329,7 +1561,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1340,6 +1572,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7368700</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>15069</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1375,7 +1623,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1386,6 +1634,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5210700</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>15147</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1421,7 +1685,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1432,6 +1696,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6065200</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>17944</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1467,7 +1747,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1478,6 +1758,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>5423300</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>15998</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1513,7 +1809,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1524,6 +1820,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5184200</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>14854</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1559,7 +1871,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1570,6 +1882,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5389600</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>15852</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1605,7 +1933,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1616,6 +1944,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5381600</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>15782</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1651,7 +1995,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1662,6 +2006,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>5427400</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>15916</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1697,7 +2057,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1708,6 +2068,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5239600</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>15231</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1743,7 +2119,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1754,6 +2130,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5408900</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>16003</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1789,7 +2181,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1800,6 +2192,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5631600</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>16612</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1835,7 +2243,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1846,6 +2254,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5124000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>14682</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1881,7 +2305,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1892,6 +2316,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>5532500</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>16272</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1927,7 +2367,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1938,6 +2378,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>5270900</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>15457</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1973,7 +2429,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1984,6 +2440,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5385100</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>15792</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2019,7 +2491,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2030,6 +2502,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5060200</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>14710</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2065,7 +2553,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2076,6 +2564,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>5889100</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>17423</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2111,7 +2615,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2122,6 +2626,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5610900</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>16551</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2157,7 +2677,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2168,6 +2688,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5095100</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>14599</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2203,7 +2739,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2214,6 +2750,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>5323000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>15656</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2249,7 +2801,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2260,6 +2812,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>5143400</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>15083</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2295,7 +2863,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2306,6 +2874,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5299800</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>15542</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2341,7 +2925,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2352,6 +2936,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5095100</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>14811</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2387,7 +2987,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2398,6 +2998,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5609400</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>16596</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2433,7 +3049,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2444,6 +3060,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>5605400</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>16535</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2479,7 +3111,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2490,6 +3122,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>5002300</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>14333</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2525,7 +3173,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2536,6 +3184,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5264400</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>15484</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2571,7 +3235,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2582,6 +3246,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5212300</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>15285</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2617,7 +3297,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2628,6 +3308,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5249600</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>15395</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2663,7 +3359,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2674,6 +3370,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>5002300</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>14542</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2709,7 +3421,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2720,6 +3432,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5577700</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>16502</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2755,7 +3483,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2766,6 +3494,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>5588800</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>16486</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2801,7 +3545,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2812,6 +3556,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5321700</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>15248</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2847,7 +3607,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2858,6 +3618,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>5206700</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>15314</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2893,7 +3669,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2904,6 +3680,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>5143400</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>15083</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2939,7 +3731,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2950,6 +3742,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>5179000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>15188</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2985,7 +3793,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -2996,6 +3804,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4973000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>14456</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3031,7 +3855,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3042,6 +3866,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5500800</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>16275</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3077,7 +3917,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3088,6 +3928,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5230500</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>15429</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3123,7 +3979,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3134,6 +3990,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4943700</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>14165</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3169,7 +4041,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3180,6 +4052,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5233700</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>15393</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3215,7 +4103,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3226,6 +4114,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>4931000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>14460</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3261,7 +4165,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3272,6 +4176,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>4935700</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>14474</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3307,7 +4227,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3318,6 +4238,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>5095800</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>14813</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3353,7 +4289,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3364,6 +4300,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5237700</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>15496</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3399,7 +4351,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3410,6 +4362,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5156100</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>15210</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3445,7 +4413,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3456,6 +4424,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>5293900</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>15169</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3491,7 +4475,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3502,6 +4486,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>5190100</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>15265</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3537,7 +4537,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3548,6 +4548,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>4889000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>14337</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3583,7 +4599,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3594,6 +4610,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>4892900</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>14349</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3629,7 +4661,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3640,6 +4672,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>5049100</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>14678</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3675,7 +4723,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3686,6 +4734,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>5187000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>15346</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3721,7 +4785,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3732,6 +4796,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>5316900</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>15684</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3767,7 +4847,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3778,6 +4858,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5144200</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>14740</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3813,7 +4909,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3824,6 +4920,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5082400</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>14948</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3859,7 +4971,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3870,6 +4982,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>5068900</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>14865</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3905,7 +5033,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3916,6 +5044,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5106100</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>14974</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3951,7 +5095,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3962,6 +5106,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>5265400</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>15262</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3997,7 +5157,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4008,6 +5168,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>5284400</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>15634</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4043,7 +5219,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4054,6 +5230,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>5404700</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>15943</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4089,7 +5281,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4100,6 +5292,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5094200</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>14597</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4135,7 +5343,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4146,6 +5354,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5311200</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>15621</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4181,7 +5405,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4192,6 +5416,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5229400</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>15335</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4227,7 +5467,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4238,6 +5478,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5269000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>15452</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4273,7 +5529,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4284,6 +5540,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>5435000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>15754</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4319,7 +5591,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4330,6 +5602,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5322100</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>15746</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4365,7 +5653,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4376,6 +5664,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>5213100</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>15378</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4411,7 +5715,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4422,6 +5726,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>5081600</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>14560</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4457,7 +5777,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4468,6 +5788,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>4982500</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>14654</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4503,7 +5839,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4514,6 +5850,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>4969000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>14572</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4549,7 +5901,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4560,6 +5912,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>5005500</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>14679</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4595,7 +5963,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4606,6 +5974,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5158400</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>14952</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4641,7 +6025,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4652,6 +6036,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5183000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>15334</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4687,7 +6087,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4698,6 +6098,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>6244600</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>18421</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4733,7 +6149,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4744,6 +6160,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>4901700</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>14045</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4779,7 +6211,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4790,6 +6222,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5268200</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>15495</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4825,7 +6273,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4836,6 +6284,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>5184000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>15202</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4871,7 +6335,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4882,6 +6346,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5225200</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>15323</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4917,7 +6397,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4928,6 +6408,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>5119600</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>14839</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4963,7 +6459,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4974,6 +6470,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5400500</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>15978</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5009,7 +6521,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5020,6 +6532,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5469800</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>16135</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5055,7 +6583,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5066,6 +6594,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>4837700</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>13862</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5101,7 +6645,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5112,6 +6656,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>4891300</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>14386</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5147,7 +6707,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5158,6 +6718,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5108600</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>14981</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5193,7 +6769,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5204,6 +6780,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>5149200</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>15100</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5239,7 +6831,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5250,6 +6842,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>4742600</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>13787</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5285,7 +6893,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5296,6 +6904,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5207000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>15405</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5331,7 +6955,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5342,6 +6966,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5142400</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>15169</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5377,7 +7017,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5388,6 +7028,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>4797000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>13745</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5423,7 +7079,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5434,6 +7090,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>4607700</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>13552</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5469,7 +7141,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5480,6 +7152,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>4834400</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>14177</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5515,7 +7203,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5526,6 +7214,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>4809200</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>14103</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5561,7 +7265,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5572,6 +7276,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>4696300</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>13652</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5607,7 +7327,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5618,6 +7338,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>5049700</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>14940</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5653,7 +7389,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5664,6 +7400,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>5955200</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>17567</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5699,7 +7451,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5710,6 +7462,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>6094600</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>17463</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5745,7 +7513,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5756,6 +7524,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>5084500</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>14954</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5791,7 +7575,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5802,6 +7586,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>4999100</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>14660</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5837,7 +7637,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5848,6 +7648,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5039600</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>14779</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5883,7 +7699,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5894,6 +7710,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>4634500</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>13472</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5929,7 +7761,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5940,6 +7772,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>5099100</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>15086</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5975,7 +7823,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -5986,6 +7834,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5991500</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>17674</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6021,7 +7885,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6032,6 +7896,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>5930400</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>16993</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6067,7 +7947,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6078,6 +7958,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>4821400</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>14181</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6113,7 +8009,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6124,6 +8020,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>5031000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>14754</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6159,7 +8071,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6170,6 +8082,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5072400</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>14875</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6205,7 +8133,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6216,6 +8144,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>4613400</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>13411</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6251,7 +8195,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6262,6 +8206,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>15089</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6297,7 +8257,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6308,6 +8268,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>4932700</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>14551</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6343,7 +8319,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6354,6 +8330,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>4689000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>13436</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6389,7 +8381,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6400,6 +8392,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>4532200</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>13330</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6435,7 +8443,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6446,6 +8454,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>4797900</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>14070</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6481,7 +8505,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6492,6 +8516,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>4789700</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>14046</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6527,7 +8567,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6538,6 +8578,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>4541900</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>13203</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6573,7 +8629,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6584,6 +8640,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>4814900</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>14245</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6619,7 +8691,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6630,6 +8702,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>4979100</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>14688</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6665,7 +8753,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6676,6 +8764,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5097400</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>14606</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6711,7 +8815,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6722,6 +8826,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>5000300</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>14707</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6757,7 +8877,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6768,6 +8888,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>4800700</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>14078</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6803,7 +8939,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6814,6 +8950,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>4953500</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>14526</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6849,7 +9001,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6860,6 +9012,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>4761000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>13800</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6895,7 +9063,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6906,6 +9074,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>4852900</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>14358</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6941,7 +9125,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6952,6 +9136,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>6058400</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>17871</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6987,7 +9187,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -6998,6 +9198,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>5060500</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>14500</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7033,7 +9249,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7044,6 +9260,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>4502900</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>13244</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7079,7 +9311,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7090,6 +9322,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>4940400</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>14488</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7125,7 +9373,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7136,6 +9384,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>4983600</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>14615</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7171,7 +9435,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7182,6 +9446,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>4898200</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>14198</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7217,7 +9497,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7228,6 +9508,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>6102800</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>18056</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7263,7 +9559,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7274,6 +9570,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>4923400</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>14523</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7309,7 +9621,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7320,6 +9632,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>4903400</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>14050</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7355,7 +9683,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7366,6 +9694,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>4726500</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>13901</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7401,7 +9745,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7412,6 +9756,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>4747900</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>13923</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7447,7 +9807,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7458,6 +9818,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>4680800</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>13727</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7493,7 +9869,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7504,6 +9880,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>4706700</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>13643</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7539,7 +9931,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7550,6 +9942,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>4691200</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>13879</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7585,7 +9993,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7596,6 +10004,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>5130200</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>17101</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7631,7 +10055,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7642,6 +10066,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>4858000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>15621</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7677,7 +10117,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7688,6 +10128,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>4349400</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>14402</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7723,7 +10179,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7734,6 +10190,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>4337200</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>14267</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7769,7 +10241,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7780,6 +10252,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>4316900</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>14247</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7815,7 +10303,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7826,6 +10314,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>5256100</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>17121</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7861,7 +10365,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7872,13 +10376,29 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>5409700</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>18032</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8028,7 +10548,7 @@
           <t>A | 381呎 (1房)
 $617万
 $16,183/呎
-(已售)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -8037,7 +10557,7 @@
           <t>C | 792呎 (3房)
 $1410万
 $17,803/呎
-(已售)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -8046,7 +10566,7 @@
           <t>E | 792呎 (3房)
 $1330万
 $16,793/呎
-(已售)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr"/>
@@ -8055,7 +10575,7 @@
           <t>G | 381呎 (1房)
 $616万
 $16,170/呎
-(已售)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -8070,7 +10590,7 @@
           <t>A | 338呎 (1房)
 $544万
 $16,102/呎
-(已售)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -8078,7 +10598,7 @@
           <t>B | 344呎 (1房)
 $524万
 $15,231/呎
-(已售)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8086,7 +10606,7 @@
           <t>C | 489呎 (2房)
 $745万
 $15,237/呎
-(已售)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -8095,7 +10615,7 @@
           <t>E | 489呎 (2房)
 $745万
 $15,236/呎
-(已售)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -8103,7 +10623,7 @@
           <t>F | 349呎 (1房)
 $524万
 $15,013/呎
-(已售)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -8111,7 +10631,7 @@
           <t>G | 339呎 (1房)
 $545万
 $16,088/呎
-(已售)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -8126,7 +10646,7 @@
           <t>A | 338呎 (1房)
 $607万
 $17,944/呎
-(已售)</t>
+(24年-02月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -8134,7 +10654,7 @@
           <t>B | 344呎 (1房)
 $521万
 $15,147/呎
-(已售)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -8142,7 +10662,7 @@
           <t>C | 489呎 (2房)
 $737万
 $15,069/呎
-(已售)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr"/>
@@ -8151,7 +10671,7 @@
           <t>E | 489呎 (2房)
 $767万
 $15,685/呎
-(已售)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -8159,7 +10679,7 @@
           <t>F | 349呎 (1房)
 $521万
 $14,928/呎
-(已售)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -8167,7 +10687,7 @@
           <t>G | 339呎 (1房)
 $580万
 $17,115/呎
-(已售)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -8182,7 +10702,7 @@
           <t>A | 338呎 (1房)
 $541万
 $16,003/呎
-(已售)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8190,7 +10710,7 @@
           <t>B | 344呎 (1房)
 $524万
 $15,231/呎
-(已售)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8198,7 +10718,7 @@
           <t>C | 341呎 (1房)
 $543万
 $15,916/呎
-(已售)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -8206,7 +10726,7 @@
           <t>D | 341呎 (1房)
 $538万
 $15,782/呎
-(已售)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -8214,7 +10734,7 @@
           <t>E | 340呎 (1房)
 $539万
 $15,852/呎
-(已售)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -8222,7 +10742,7 @@
           <t>F | 349呎 (1房)
 $518万
 $14,854/呎
-(已售)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -8230,7 +10750,7 @@
           <t>G | 339呎 (1房)
 $542万
 $15,998/呎
-(已售)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -8245,7 +10765,7 @@
           <t>A | 338呎 (1房)
 $589万
 $17,423/呎
-(已售)</t>
+(24年-02月-13日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8253,7 +10773,7 @@
           <t>B | 344呎 (1房)
 $506万
 $14,710/呎
-(已售)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8261,7 +10781,7 @@
           <t>C | 341呎 (1房)
 $539万
 $15,792/呎
-(已售)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -8269,7 +10789,7 @@
           <t>D | 341呎 (1房)
 $527万
 $15,457/呎
-(已售)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -8277,7 +10797,7 @@
           <t>E | 340呎 (1房)
 $553万
 $16,272/呎
-(已售)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -8285,7 +10805,7 @@
           <t>F | 349呎 (1房)
 $512万
 $14,682/呎
-(已售)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -8293,7 +10813,7 @@
           <t>G | 339呎 (1房)
 $563万
 $16,612/呎
-(已售)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -8308,7 +10828,7 @@
           <t>A | 338呎 (1房)
 $561万
 $16,596/呎
-(已售)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -8316,7 +10836,7 @@
           <t>B | 344呎 (1房)
 $510万
 $14,811/呎
-(已售)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8324,7 +10844,7 @@
           <t>C | 341呎 (1房)
 $530万
 $15,542/呎
-(已售)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -8332,7 +10852,7 @@
           <t>D | 341呎 (1房)
 $514万
 $15,083/呎
-(已售)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -8340,7 +10860,7 @@
           <t>E | 340呎 (1房)
 $532万
 $15,656/呎
-(已售)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -8348,7 +10868,7 @@
           <t>F | 349呎 (1房)
 $510万
 $14,599/呎
-(已售)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -8356,7 +10876,7 @@
           <t>G | 339呎 (1房)
 $561万
 $16,551/呎
-(已售)</t>
+(24年-12月-26日)</t>
         </is>
       </c>
     </row>
@@ -8371,7 +10891,7 @@
           <t>A | 338呎 (1房)
 $558万
 $16,502/呎
-(已售)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8379,7 +10899,7 @@
           <t>B | 344呎 (1房)
 $500万
 $14,542/呎
-(已售)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -8387,7 +10907,7 @@
           <t>C | 341呎 (1房)
 $525万
 $15,395/呎
-(已售)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -8395,7 +10915,7 @@
           <t>D | 341呎 (1房)
 $521万
 $15,285/呎
-(已售)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -8403,7 +10923,7 @@
           <t>E | 340呎 (1房)
 $526万
 $15,484/呎
-(已售)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -8411,7 +10931,7 @@
           <t>F | 349呎 (1房)
 $500万
 $14,333/呎
-(已售)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -8419,7 +10939,7 @@
           <t>G | 339呎 (1房)
 $561万
 $16,535/呎
-(已售)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -8434,7 +10954,7 @@
           <t>A | 338呎 (1房)
 $550万
 $16,275/呎
-(已售)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8442,7 +10962,7 @@
           <t>B | 344呎 (1房)
 $497万
 $14,456/呎
-(已售)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8450,7 +10970,7 @@
           <t>C | 341呎 (1房)
 $518万
 $15,188/呎
-(已售)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -8458,7 +10978,7 @@
           <t>D | 341呎 (1房)
 $514万
 $15,083/呎
-(已售)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -8466,7 +10986,7 @@
           <t>E | 340呎 (1房)
 $521万
 $15,314/呎
-(已售)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -8474,7 +10994,7 @@
           <t>F | 349呎 (1房)
 $532万
 $15,248/呎
-(已售)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -8482,7 +11002,7 @@
           <t>G | 339呎 (1房)
 $559万
 $16,486/呎
-(已售)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -8497,7 +11017,7 @@
           <t>A | 338呎 (1房)
 $524万
 $15,496/呎
-(已售)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8505,7 +11025,7 @@
           <t>B | 344呎 (1房)
 $510万
 $14,813/呎
-(已售)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -8513,7 +11033,7 @@
           <t>C | 341呎 (1房)
 $494万
 $14,474/呎
-(已售)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -8521,7 +11041,7 @@
           <t>D | 341呎 (1房)
 $493万
 $14,460/呎
-(已售)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -8529,7 +11049,7 @@
           <t>E | 340呎 (1房)
 $523万
 $15,393/呎
-(已售)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -8537,7 +11057,7 @@
           <t>F | 349呎 (1房)
 $494万
 $14,165/呎
-(已售)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -8545,7 +11065,7 @@
           <t>G | 339呎 (1房)
 $523万
 $15,429/呎
-(已售)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -8560,7 +11080,7 @@
           <t>A | 338呎 (1房)
 $519万
 $15,346/呎
-(已售)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8568,7 +11088,7 @@
           <t>B | 344呎 (1房)
 $505万
 $14,678/呎
-(已售)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8576,7 +11096,7 @@
           <t>C | 341呎 (1房)
 $489万
 $14,349/呎
-(已售)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -8584,7 +11104,7 @@
           <t>D | 341呎 (1房)
 $489万
 $14,337/呎
-(已售)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -8592,7 +11112,7 @@
           <t>E | 340呎 (1房)
 $519万
 $15,265/呎
-(已售)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -8600,7 +11120,7 @@
           <t>F | 349呎 (1房)
 $529万
 $15,169/呎
-(已售)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -8608,7 +11128,7 @@
           <t>G | 339呎 (1房)
 $516万
 $15,210/呎
-(已售)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -8623,7 +11143,7 @@
           <t>A | 338呎 (1房)
 $528万
 $15,634/呎
-(已售)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8631,7 +11151,7 @@
           <t>B | 345呎 (1房)
 $527万
 $15,262/呎
-(已售)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8639,7 +11159,7 @@
           <t>C | 341呎 (1房)
 $511万
 $14,974/呎
-(已售)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -8647,7 +11167,7 @@
           <t>D | 341呎 (1房)
 $507万
 $14,865/呎
-(已售)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -8655,7 +11175,7 @@
           <t>E | 340呎 (1房)
 $508万
 $14,948/呎
-(已售)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -8663,7 +11183,7 @@
           <t>F | 349呎 (1房)
 $514万
 $14,740/呎
-(已售)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -8671,7 +11191,7 @@
           <t>G | 339呎 (1房)
 $532万
 $15,684/呎
-(已售)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -8686,7 +11206,7 @@
           <t>A | 338呎 (1房)
 $532万
 $15,746/呎
-(已售)</t>
+(24年-01月-30日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -8694,7 +11214,7 @@
           <t>B | 345呎 (1房)
 $544万
 $15,754/呎
-(已售)</t>
+(24年-02月-15日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8702,7 +11222,7 @@
           <t>C | 341呎 (1房)
 $527万
 $15,452/呎
-(已售)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -8710,7 +11230,7 @@
           <t>D | 341呎 (1房)
 $523万
 $15,335/呎
-(已售)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -8718,7 +11238,7 @@
           <t>E | 340呎 (1房)
 $531万
 $15,621/呎
-(已售)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -8726,7 +11246,7 @@
           <t>F | 349呎 (1房)
 $509万
 $14,597/呎
-(已售)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -8734,7 +11254,7 @@
           <t>G | 339呎 (1房)
 $540万
 $15,943/呎
-(已售)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -8749,7 +11269,7 @@
           <t>A | 338呎 (1房)
 $518万
 $15,334/呎
-(已售)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -8757,7 +11277,7 @@
           <t>B | 345呎 (1房)
 $516万
 $14,952/呎
-(已售)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8765,7 +11285,7 @@
           <t>C | 341呎 (1房)
 $501万
 $14,679/呎
-(已售)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -8773,7 +11293,7 @@
           <t>D | 341呎 (1房)
 $497万
 $14,572/呎
-(已售)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8781,7 +11301,7 @@
           <t>E | 340呎 (1房)
 $498万
 $14,654/呎
-(已售)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -8789,7 +11309,7 @@
           <t>F | 349呎 (1房)
 $508万
 $14,560/呎
-(已售)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -8797,7 +11317,7 @@
           <t>G | 339呎 (1房)
 $521万
 $15,378/呎
-(已售)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -8812,7 +11332,7 @@
           <t>A | 338呎 (1房)
 $540万
 $15,978/呎
-(已售)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -8820,7 +11340,7 @@
           <t>B | 345呎 (1房)
 $512万
 $14,839/呎
-(已售)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8828,7 +11348,7 @@
           <t>C | 341呎 (1房)
 $523万
 $15,323/呎
-(已售)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -8836,7 +11356,7 @@
           <t>D | 341呎 (1房)
 $518万
 $15,202/呎
-(已售)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -8844,7 +11364,7 @@
           <t>E | 340呎 (1房)
 $527万
 $15,495/呎
-(已售)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -8852,7 +11372,7 @@
           <t>F | 349呎 (1房)
 $490万
 $14,045/呎
-(已售)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -8860,7 +11380,7 @@
           <t>G | 339呎 (1房)
 $624万
 $18,421/呎
-(已售)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -8875,7 +11395,7 @@
           <t>A | 338呎 (1房)
 $521万
 $15,405/呎
-(已售)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -8883,7 +11403,7 @@
           <t>B | 344呎 (1房)
 $474万
 $13,787/呎
-(已售)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -8891,7 +11411,7 @@
           <t>C | 341呎 (1房)
 $515万
 $15,100/呎
-(已售)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -8899,7 +11419,7 @@
           <t>D | 341呎 (1房)
 $511万
 $14,981/呎
-(已售)</t>
+(24年-02月-07日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -8907,7 +11427,7 @@
           <t>E | 340呎 (1房)
 $489万
 $14,386/呎
-(已售)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -8915,7 +11435,7 @@
           <t>F | 349呎 (1房)
 $484万
 $13,862/呎
-(已售)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -8923,7 +11443,7 @@
           <t>G | 339呎 (1房)
 $547万
 $16,135/呎
-(已售)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -8938,7 +11458,7 @@
           <t>A | 338呎 (1房)
 $505万
 $14,940/呎
-(已售)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -8946,7 +11466,7 @@
           <t>B | 344呎 (1房)
 $470万
 $13,652/呎
-(已售)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8954,7 +11474,7 @@
           <t>C | 341呎 (1房)
 $481万
 $14,103/呎
-(已售)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8962,7 +11482,7 @@
           <t>D | 341呎 (1房)
 $483万
 $14,177/呎
-(已售)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8970,7 +11490,7 @@
           <t>E | 340呎 (1房)
 $461万
 $13,552/呎
-(已售)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -8978,7 +11498,7 @@
           <t>F | 349呎 (1房)
 $480万
 $13,745/呎
-(已售)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -8986,7 +11506,7 @@
           <t>G | 339呎 (1房)
 $514万
 $15,169/呎
-(已售)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -9001,7 +11521,7 @@
           <t>A | 338呎 (1房)
 $510万
 $15,086/呎
-(已售)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -9009,7 +11529,7 @@
           <t>B | 344呎 (1房)
 $463万
 $13,472/呎
-(已售)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -9017,7 +11537,7 @@
           <t>C | 341呎 (1房)
 $504万
 $14,779/呎
-(已售)</t>
+(24年-02月-14日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -9025,7 +11545,7 @@
           <t>D | 341呎 (1房)
 $500万
 $14,660/呎
-(已售)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -9033,7 +11553,7 @@
           <t>E | 340呎 (1房)
 $508万
 $14,954/呎
-(已售)</t>
+(24年-02月-28日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -9041,7 +11561,7 @@
           <t>F | 349呎 (1房)
 $609万
 $17,463/呎
-(已售)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -9049,7 +11569,7 @@
           <t>G | 339呎 (1房)
 $596万
 $17,567/呎
-(已售)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -9064,7 +11584,7 @@
           <t>A | 338呎 (1房)
 $510万
 $15,089/呎
-(已售)</t>
+(24年-02月-21日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -9072,7 +11592,7 @@
           <t>B | 344呎 (1房)
 $461万
 $13,411/呎
-(已售)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9080,7 +11600,7 @@
           <t>C | 341呎 (1房)
 $507万
 $14,875/呎
-(已售)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -9088,7 +11608,7 @@
           <t>D | 341呎 (1房)
 $503万
 $14,754/呎
-(已售)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -9096,7 +11616,7 @@
           <t>E | 340呎 (1房)
 $482万
 $14,181/呎
-(已售)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -9104,7 +11624,7 @@
           <t>F | 349呎 (1房)
 $593万
 $16,993/呎
-(已售)</t>
+(23年-09月-05日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -9112,7 +11632,7 @@
           <t>G | 339呎 (1房)
 $599万
 $17,674/呎
-(已售)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -9127,7 +11647,7 @@
           <t>A | 338呎 (1房)
 $481万
 $14,245/呎
-(已售)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -9135,7 +11655,7 @@
           <t>B | 344呎 (1房)
 $454万
 $13,203/呎
-(已售)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -9143,7 +11663,7 @@
           <t>C | 341呎 (1房)
 $479万
 $14,046/呎
-(已售)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -9151,7 +11671,7 @@
           <t>D | 341呎 (1房)
 $480万
 $14,070/呎
-(已售)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -9159,7 +11679,7 @@
           <t>E | 340呎 (1房)
 $453万
 $13,330/呎
-(已售)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -9167,7 +11687,7 @@
           <t>F | 349呎 (1房)
 $469万
 $13,436/呎
-(已售)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -9175,7 +11695,7 @@
           <t>G | 339呎 (1房)
 $493万
 $14,551/呎
-(已售)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -9190,7 +11710,7 @@
           <t>A | 338呎 (1房)
 $485万
 $14,358/呎
-(已售)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9198,7 +11718,7 @@
           <t>B | 345呎 (1房)
 $476万
 $13,800/呎
-(已售)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9206,7 +11726,7 @@
           <t>C | 341呎 (1房)
 $495万
 $14,526/呎
-(已售)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -9214,7 +11734,7 @@
           <t>D | 341呎 (1房)
 $480万
 $14,078/呎
-(已售)</t>
+(24年-01月-30日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -9222,7 +11742,7 @@
           <t>E | 340呎 (1房)
 $500万
 $14,707/呎
-(已售)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -9230,7 +11750,7 @@
           <t>F | 349呎 (1房)
 $510万
 $14,606/呎
-(已售)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -9238,7 +11758,7 @@
           <t>G | 339呎 (1房)
 $498万
 $14,688/呎
-(已售)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -9253,7 +11773,7 @@
           <t>A | 338呎 (1房)
 $610万
 $18,056/呎
-(已售)</t>
+(23年-04月-05日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -9261,7 +11781,7 @@
           <t>B | 345呎 (1房)
 $490万
 $14,198/呎
-(已售)</t>
+(24年-02月-20日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -9269,7 +11789,7 @@
           <t>C | 341呎 (1房)
 $498万
 $14,615/呎
-(已售)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -9277,7 +11797,7 @@
           <t>D | 341呎 (1房)
 $494万
 $14,488/呎
-(已售)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -9285,7 +11805,7 @@
           <t>E | 340呎 (1房)
 $450万
 $13,244/呎
-(已售)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -9293,7 +11813,7 @@
           <t>F | 349呎 (1房)
 $506万
 $14,500/呎
-(已售)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -9301,7 +11821,7 @@
           <t>G | 339呎 (1房)
 $606万
 $17,871/呎
-(已售)</t>
+(23年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -9316,7 +11836,7 @@
           <t>A | 338呎 (1房)
 $469万
 $13,879/呎
-(已售)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -9324,7 +11844,7 @@
           <t>B | 345呎 (1房)
 $471万
 $13,643/呎
-(已售)</t>
+(24年-01月-16日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9332,7 +11852,7 @@
           <t>C | 341呎 (1房)
 $468万
 $13,727/呎
-(已售)</t>
+(24年-01月-24日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -9340,7 +11860,7 @@
           <t>D | 341呎 (1房)
 $475万
 $13,923/呎
-(已售)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -9348,7 +11868,7 @@
           <t>E | 340呎 (1房)
 $473万
 $13,901/呎
-(已售)</t>
+(24年-01月-23日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -9356,7 +11876,7 @@
           <t>F | 349呎 (1房)
 $490万
 $14,050/呎
-(已售)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -9364,7 +11884,7 @@
           <t>G | 339呎 (1房)
 $492万
 $14,523/呎
-(已售)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -9379,7 +11899,7 @@
           <t>A | 300呎 (1房)
 $541万
 $18,032/呎
-(已售)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -9387,7 +11907,7 @@
           <t>B | 307呎 (1房)
 $526万
 $17,121/呎
-(已售)</t>
+(25年-03月-09日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -9395,7 +11915,7 @@
           <t>C | 303呎 (1房)
 $432万
 $14,247/呎
-(已售)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -9403,7 +11923,7 @@
           <t>D | 304呎 (1房)
 $434万
 $14,267/呎
-(已售)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -9411,7 +11931,7 @@
           <t>E | 302呎 (1房)
 $435万
 $14,402/呎
-(已售)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -9419,7 +11939,7 @@
           <t>F | 311呎 (1房)
 $486万
 $15,621/呎
-(已售)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -9427,7 +11947,7 @@
           <t>G | 300呎 (1房)
 $513万
 $17,101/呎
-(已售)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
     </row>
